--- a/rulebook-examples/acme-llc/xlsx/rulebook.xlsx
+++ b/rulebook-examples/acme-llc/xlsx/rulebook.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customers" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBVersions" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERBCustomizations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__meta__" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -161,7 +162,7 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Identifier for the customers.</t>
+        <t>Identifier for the cusfdsfdstomers.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
@@ -174,14 +175,49 @@
         <t>First Name of the customer - used to make the full name</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>Last Name of the customer - used to make the full name</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>Full name is computed from the first and last name of the customer</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>ERB Rulebook</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>The metadata key (e.g. 'tagline', 'motif_palette', 'substrates'). Unique within the table.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Identifier for this metadata entry. Mirrors MetaKey so the row is addressable by Name like every other table.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>How to interpret the value columns: 'string' (use StringValue), 'object' (parse JsonValue as JSON object), 'array' (parse JsonValue as JSON array).</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Plain string value. Populated when ValueType == 'string'; null otherwise.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>JSON-encoded value. Populated when ValueType == 'object' or 'array'; null when ValueType == 'string'.</t>
       </text>
     </comment>
   </commentList>
@@ -477,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -486,6 +522,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,10 +548,15 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Initials</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>LastName</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>FullName</t>
         </is>
@@ -540,13 +582,17 @@
           <t>Bobby</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3">
+        <f>LEFT($D2, 1) &amp; LEFT($F2, 1)</f>
+        <v/>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Smith</t>
         </is>
       </c>
-      <c r="F2" s="3">
-        <f>$E2 &amp; ", " &amp; $D2</f>
+      <c r="G2" s="3">
+        <f>$D2 &amp; " " &amp; $F2</f>
         <v/>
       </c>
     </row>
@@ -570,13 +616,17 @@
           <t>Jimmy</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3">
+        <f>LEFT($D3, 1) &amp; LEFT($F3, 1)</f>
+        <v/>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Doe</t>
         </is>
       </c>
-      <c r="F3" s="3">
-        <f>$E3 &amp; ", " &amp; $D3</f>
+      <c r="G3" s="3">
+        <f>$D3 &amp; " " &amp; $F3</f>
         <v/>
       </c>
     </row>
@@ -600,13 +650,17 @@
           <t>Mary</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3">
+        <f>LEFT($D4, 1) &amp; LEFT($F4, 1)</f>
+        <v/>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Jones</t>
         </is>
       </c>
-      <c r="F4" s="3">
-        <f>$E4 &amp; ", " &amp; $D4</f>
+      <c r="G4" s="3">
+        <f>$D4 &amp; " " &amp; $F4</f>
         <v/>
       </c>
     </row>
@@ -959,4 +1013,273 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MetaKey</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ValueType</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>StringValue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>JsonValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>tagline</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>$A2</f>
+        <v/>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>A one-table customer ledger, filed last-name-first.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>motif</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>$A3</f>
+        <v/>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>legal-pad</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>motif_palette</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>$A4</f>
+        <v/>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>{"primary": "#a8941f", "accent": "#4a6741", "ink": "#1f1c0a"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>description_rich</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>$A5</f>
+        <v/>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>ACME, LLC is the **leanest possible rulebook with real wiring** — a single business table (`Customers`) and two calculated fields that re-derive themselves from raw inputs. Unlike its larger cousin ACME Corporation, there are no projects, no roles, no approval workflows: just a client ledger where every customer carries *two* identifiers at once. `Name` is a slug minted from the email address; `FullName` is the same person reformatted last-name-first, courtroom-style. Edit one raw field and both derived labels rewrite themselves in every substrate — Postgres view, Python class, Excel cell, OWL ontology — with zero application code.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>use_cases</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>$A6</f>
+        <v/>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>["**Rename a customer.** Change `jane-smith-email-com`'s `FirstName` from `Bobby` to `Robert` and watch `FullName` recompute to `Smith, Robert` on the next read — same row, same id, new label.", "**Update an email address.** Edit `john.doe@email.com` to `j.doe@example.com`; the `Name` slug re-derives to `j.doe-example.com` automatically in every substrate.", "**Add a new customer with just the three raw fields** (`EmailAddress`, `FirstName`, `LastName`) and let the rulebook fill in `Name` and `FullName` — no insert triggers, no application logic.", "**Ask the same question of two substrates.** *\"Sort customers alphabetically by surname.\"* The Postgres view and the Python module both return Doe, Jones, Smith — without anyone writing a sort key.", "**Flip the formula in the rulebook** from `LastName &amp; \", \" &amp; FirstName` to `FirstName &amp; \" \" &amp; LastName` and re-run `effortless build`; every substrate now prints western-style names instead of legal-style, with no migration."]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>signature_rows</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>$A7</f>
+        <v/>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>[{"entity": "Customers", "ids": ["jane-smith-email-com", "john-doe-email-com", "emily-jones-email-com"]}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>journal_seed</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>$A8</f>
+        <v/>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Three customers on file. Each one filed twice — once by email-slug, once by surname-first — and both labels stay in lockstep with the raw fields.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>substrates</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>$A9</f>
+        <v/>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>[{"key": "postgres", "important": true, "chip_label": "Postgres"}, {"key": "excel", "important": true, "chip_label": "Excel"}, {"key": "python", "important": false, "chip_label": "Python"}, {"key": "owl", "important": false, "chip_label": "OWL"}, {"key": "csv", "important": false, "chip_label": "CSV"}]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CMCC_Summary</t>
+        </is>
+      </c>
+      <c r="B10" s="3">
+        <f>$A10</f>
+        <v/>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Airtable export with schema-first type mapping: Schemas, Data, Relationships (FK links), Lookups (INDEX/MATCH), Aggregations (SUMIFS/COUNTIFS/Rollups), and Calculated fields (formulas) in Excel dialect. Field types are determined from Airtable's schema metadata FIRST (no coercion); the build FAILS if metadata is unavailable rather than silently inferring from formula/data analysis.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>conversion_metadata</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>$A11</f>
+        <v/>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>{"source_base_id": "appWrXPvXbkgQGOxt", "table_count": 3, "tool_version": "2.0.0", "field_type_mapping": "checkbox→boolean, number→number/integer, multipleRecordLinks→relationship, multipleLookupValues→lookup, rollup→aggregation, count→aggregation, formula→calculated", "export_mode": "schema_first_type_mapping", "type_inference": {"enabled": true, "priority": "airtable_metadata (NO COERCION) → formula_analysis → reference_resolution → data_analysis (last-resort inference; build SHOULD FAIL rather than silently use this)", "airtable_type_mapping": "checkbox→boolean, singleLineText→string, multilineText→string, number→number/integer, datetime→datetime, singleSelect→string, email→string, url→string, phoneNumber→string", "data_coercion_hierarchy": "Only invoked when Airtable schema is unavailable (which SHOULD make the build fail). Coercion order: datetime → number → integer → boolean → base64 → json → string", "nullable_support": true, "error_value_handling": "#NUM!, #ERROR!, #N/A, #REF!, #DIV/0!, #VALUE!, #NAME? are treated as NULL"}}</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/rulebook-examples/acme-llc/xlsx/rulebook.xlsx
+++ b/rulebook-examples/acme-llc/xlsx/rulebook.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1278,6 +1278,28 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>narrative_drift_lesson</t>
+        </is>
+      </c>
+      <c r="B12" s="3">
+        <f>$A12</f>
+        <v/>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>**The point of this demo is the asymmetry between code and prose.** Flip `FullName` from `LastName &amp; ", " &amp; FirstName` (legal-style, surname-first) to `FirstName &amp; " " &amp; LastName` (western order) and re-run `effortless build`: every *executable* artifact follows along instantly and for free — the Postgres view, Python class, Go SDK, Excel/CSV, OWL, the rendered RuleSpeak DRs and section-4 expression all re-derive from the single formula and stay correct. But every *hand-written* narrative about the rules goes stale from one moment to the next — `description_rich`, `explanation_rich`, `journal_seed`, the seed `FullName` values baked into the Customers rows, and any prose README still say "Smith, Bobby / courtroom-style" even though the formula now computes "Bobby Smith". That staleness is INTENTIONAL and left in place on purpose: it is the live exhibit. Computed code follows the SSoT; comments and narrative cannot. The only narrative that can keep up is one that is itself regenerated from the rulebook (e.g. an LLM-generated README), not hand-maintained. Do not "fix" the stale narrative or seed values to match the formula — doing so erases the demonstration.</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/rulebook-examples/acme-llc/xlsx/rulebook.xlsx
+++ b/rulebook-examples/acme-llc/xlsx/rulebook.xlsx
@@ -162,17 +162,22 @@
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Identifier for the cusfdsfdstomers.</t>
+        <t>Identifier for the customer.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Thec ustomers email address</t>
+        <t>The customer's email address</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>First Name of the customer - used to make the full name</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Customer initials — the first letter of FirstName followed by the first letter of LastName.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -1251,7 +1256,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Airtable export with schema-first type mapping: Schemas, Data, Relationships (FK links), Lookups (INDEX/MATCH), Aggregations (SUMIFS/COUNTIFS/Rollups), and Calculated fields (formulas) in Excel dialect. Field types are determined from Airtable's schema metadata FIRST (no coercion); the build FAILS if metadata is unavailable rather than silently inferring from formula/data analysis.</t>
+          <t>Airtable export with schema-first type mapping. This lean rulebook is a single business table (Customers) of raw fields plus Calculated fields (formulas in Excel dialect); it uses no Relationships, Lookups, or Aggregations. Field types are determined from Airtable's schema metadata FIRST (no coercion); the build FAILS if metadata is unavailable rather than silently inferring from formula/data analysis.</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1274,7 +1279,7 @@
       <c r="D11" s="2" t="inlineStr"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>{"source_base_id": "appWrXPvXbkgQGOxt", "table_count": 3, "tool_version": "2.0.0", "field_type_mapping": "checkbox→boolean, number→number/integer, multipleRecordLinks→relationship, multipleLookupValues→lookup, rollup→aggregation, count→aggregation, formula→calculated", "export_mode": "schema_first_type_mapping", "type_inference": {"enabled": true, "priority": "airtable_metadata (NO COERCION) → formula_analysis → reference_resolution → data_analysis (last-resort inference; build SHOULD FAIL rather than silently use this)", "airtable_type_mapping": "checkbox→boolean, singleLineText→string, multilineText→string, number→number/integer, datetime→datetime, singleSelect→string, email→string, url→string, phoneNumber→string", "data_coercion_hierarchy": "Only invoked when Airtable schema is unavailable (which SHOULD make the build fail). Coercion order: datetime → number → integer → boolean → base64 → json → string", "nullable_support": true, "error_value_handling": "#NUM!, #ERROR!, #N/A, #REF!, #DIV/0!, #VALUE!, #NAME? are treated as NULL"}}</t>
+          <t>{"source_base_id": "appWrXPvXbkgQGOxt", "table_count": 4, "tool_version": "2.0.0", "field_type_mapping": "checkbox→boolean, number→number/integer, multipleRecordLinks→relationship, multipleLookupValues→lookup, rollup→aggregation, count→aggregation, formula→calculated", "export_mode": "schema_first_type_mapping", "type_inference": {"enabled": true, "priority": "airtable_metadata (NO COERCION) → formula_analysis → reference_resolution → data_analysis (last-resort inference; build SHOULD FAIL rather than silently use this)", "airtable_type_mapping": "checkbox→boolean, singleLineText→string, multilineText→string, number→number/integer, datetime→datetime, singleSelect→string, email→string, url→string, phoneNumber→string", "data_coercion_hierarchy": "Only invoked when Airtable schema is unavailable (which SHOULD make the build fail). Coercion order: datetime → number → integer → boolean → base64 → json → string", "nullable_support": true, "error_value_handling": "#NUM!, #ERROR!, #N/A, #REF!, #DIV/0!, #VALUE!, #NAME? are treated as NULL"}}</t>
         </is>
       </c>
     </row>
